--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,10 +1579,6 @@
   </si>
   <si>
     <t>Observation.derivedFrom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|ImagingSelection|QuestionnaireResponse|Observation|MolecularSequence|GenomicStudy)
-</t>
   </si>
   <si>
     <t>Related resource from which the observation is made</t>
@@ -9420,10 +9416,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9435,16 +9431,16 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9521,7 +9517,7 @@
         <v>494</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9529,10 +9525,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9558,16 +9554,16 @@
         <v>178</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9616,7 +9612,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9640,10 +9636,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -9651,10 +9647,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9769,10 +9765,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9889,10 +9885,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10011,10 +10007,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10040,13 +10036,13 @@
         <v>233</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>248</v>
@@ -10077,11 +10073,11 @@
         <v>394</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10098,7 +10094,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>93</v>
@@ -10119,7 +10115,7 @@
         <v>252</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>254</v>
@@ -10133,10 +10129,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10162,13 +10158,13 @@
         <v>338</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>340</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>342</v>
@@ -10220,7 +10216,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10241,7 +10237,7 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>345</v>
@@ -10255,10 +10251,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10284,13 +10280,13 @@
         <v>233</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>364</v>
@@ -10342,7 +10338,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10377,10 +10373,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10464,7 +10460,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10499,10 +10495,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10528,10 +10524,10 @@
         <v>83</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>438</v>
@@ -10586,7 +10582,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/arv-regimen-change</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-arv-regimen-change</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1122,7 +1122,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-reason-arv-regimen-change</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
@@ -2041,7 +2041,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.8984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="117.18359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/arv-regimen-change</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-arv-regimen-change</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1122,7 +1122,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-reason-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-arv-regimen-change</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
@@ -2041,7 +2041,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="117.18359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.8984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/arv-regimen-change</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-arv-regimen-change</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1122,7 +1122,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-reason-arv-regimen-change</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
@@ -2041,7 +2041,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.8984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="112.8515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/arv-regimen-change</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-arv-regimen-change</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1122,7 +1122,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-reason-arv-regimen-change</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-arv-regimen-change</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
@@ -2041,7 +2041,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="112.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.8984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
